--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00858-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00858-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A63593F-E14F-46CF-9DBD-4CB7FD680569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30EC9601-7623-482F-BB91-54B2BABB6E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{60BFC68C-4087-40FA-BE58-5986BAD7FC1C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D956E212-FBE3-4FB9-B0E9-7BEC49F4CE3F}"/>
   </bookViews>
   <sheets>
     <sheet name="00858-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1540,25 +1540,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCC5B31-0C4A-4C05-B79D-09DD407CDD83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC0B5A7-739E-4690-A7FE-A57F45C6CE14}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1792,7 +1792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>9.94</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
         <v>51</v>
       </c>
